--- a/data/trans_camb/P15B_3_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P15B_3_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-39,33</t>
+          <t>-37,49</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-18,1</t>
+          <t>-17,51</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-71,96; -6,63</t>
+          <t>-71,92; -4,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-60,51; 9,34</t>
+          <t>-62,88; 9,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-71,15; -4,68</t>
+          <t>-70,05; -3,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,88</t>
+          <t>0,0; 21,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 38,4</t>
+          <t>8,29; 37,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 19,45</t>
+          <t>3,34; 20,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,13; -0,25</t>
+          <t>-46,26; 0,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 14,55</t>
+          <t>-33,76; 15,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 1,23</t>
+          <t>-43,7; 4,39</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-76,87%</t>
+          <t>-73,29%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-62,38%</t>
+          <t>-60,31%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-94,93; -15,11</t>
+          <t>-95,71; -13,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,91; 44,93</t>
+          <t>-89,71; 55,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-94,85; -0,06</t>
+          <t>-93,66; -4,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,4; 28,97</t>
+          <t>-89,13; 53,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,03; 130,78</t>
+          <t>-71,32; 175,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-88,83; 28,4</t>
+          <t>-84,76; 57,31</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23,22</t>
+          <t>22,66</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-2,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 23,41</t>
+          <t>0,0; 21,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 40,76</t>
+          <t>5,23; 39,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 55,64</t>
+          <t>7,68; 48,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-57,25; 0,0</t>
+          <t>-56,43; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 18,28</t>
+          <t>-46,45; 19,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,17; 0,0</t>
+          <t>-55,78; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 4,71</t>
+          <t>-30,69; 4,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 20,69</t>
+          <t>-20,63; 18,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 13,21</t>
+          <t>-24,72; 12,02</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-16,02%</t>
+          <t>-19,25%</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>11,4</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,29</t>
+          <t>11,69</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>5,79</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 25,17</t>
+          <t>-17,44; 24,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 23,2</t>
+          <t>-24,56; 21,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 30,02</t>
+          <t>-13,48; 35,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 29,94</t>
+          <t>2,14; 29,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 12,35</t>
+          <t>-19,88; 12,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 12,49</t>
+          <t>-23,57; 11,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 19,3</t>
+          <t>-14,71; 22,99</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,54; —</t>
+          <t>-52,46; 560,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,51; 867,68</t>
+          <t>-55,09; 653,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,46; 307,63</t>
+          <t>-68,07; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,17; 626,79</t>
+          <t>-62,41; —</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>12,58</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>7,53</t>
         </is>
       </c>
     </row>
@@ -1325,17 +1325,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-45,52; -2,94</t>
+          <t>-45,87; -2,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 9,89</t>
+          <t>-39,7; 6,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 51,3</t>
+          <t>-19,48; 43,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 21,09</t>
+          <t>2,35; 21,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,12</t>
+          <t>0,0; 17,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,65; -0,35</t>
+          <t>-31,65; 0,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 7,16</t>
+          <t>-25,05; 6,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 33,42</t>
+          <t>-11,84; 33,72</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 28,03</t>
+          <t>-100,0; 24,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-87,35; 116,18</t>
+          <t>-91,19; 92,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 421,61</t>
+          <t>-60,96; 392,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 46,72</t>
+          <t>-100,0; 114,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-80,9; 119,13</t>
+          <t>-79,51; 137,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 563,06</t>
+          <t>-58,18; 434,61</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-30,1</t>
+          <t>-29,51</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-15,59</t>
+          <t>-14,97</t>
         </is>
       </c>
     </row>
@@ -1541,27 +1541,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-57,39; 38,37</t>
+          <t>-60,42; 34,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-58,76; 32,97</t>
+          <t>-58,97; 28,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-74,37; 14,57</t>
+          <t>-73,47; 16,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 0,0</t>
+          <t>-57,37; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 73,67</t>
+          <t>-28,41; 72,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 6,1</t>
+          <t>-44,01; 7,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 31,91</t>
+          <t>-32,36; 31,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 20,36</t>
+          <t>-43,9; 22,57</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-70,1%</t>
+          <t>-68,72%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-56,64%</t>
+          <t>-54,4%</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-82,07; —</t>
+          <t>-85,52; 320,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-87,11; —</t>
+          <t>-86,47; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-92,11; 73,57</t>
+          <t>-89,13; 204,35</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-79,69; 427,92</t>
+          <t>-79,68; 324,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-38,66</t>
+          <t>-41,02</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-7,71</t>
+          <t>-7,78</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-20,91</t>
+          <t>-22,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-77,08; -5,85</t>
+          <t>-76,71; -6,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-84,57; -12,48</t>
+          <t>-82,8; -11,52</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-70,1; 1,97</t>
+          <t>-71,78; -2,18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 15,88</t>
+          <t>-27,83; 15,85</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 0,0</t>
+          <t>-39,97; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 3,85</t>
+          <t>-37,93; 3,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 1,94</t>
+          <t>-45,99; 0,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-58,37; -8,72</t>
+          <t>-56,48; -10,28</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-53,58; 0,59</t>
+          <t>-51,27; -0,97</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-57,68%</t>
+          <t>-61,2%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-79,32%</t>
+          <t>-80,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-58,31%</t>
+          <t>-62,35%</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-87,49; -20,08</t>
+          <t>-88,46; -12,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-95,4; -30,64</t>
+          <t>-94,56; -30,45</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-83,15; 7,11</t>
+          <t>-82,19; -0,62</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-83,41; 30,09</t>
+          <t>-82,65; 7,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-96,31; -42,33</t>
+          <t>-96,12; -43,31</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-87,72; 14,29</t>
+          <t>-86,06; 6,53</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-22,72</t>
+          <t>-25,92</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-12,85</t>
+          <t>-13,77</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-19,43</t>
+          <t>-21,34</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 27,33</t>
+          <t>-18,9; 27,14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 2,96</t>
+          <t>-47,34; 2,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-46,12; 0,74</t>
+          <t>-47,46; -3,78</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 1,12</t>
+          <t>-39,54; 1,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-46,1; -1,56</t>
+          <t>-45,04; -1,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 6,31</t>
+          <t>-41,27; 4,86</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 9,22</t>
+          <t>-23,06; 8,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-39,48; -5,42</t>
+          <t>-40,28; -5,65</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-36,11; -4,61</t>
+          <t>-38,35; -7,79</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-58,88%</t>
+          <t>-67,18%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-54,66%</t>
+          <t>-58,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-59,77%</t>
+          <t>-65,65%</t>
         </is>
       </c>
     </row>
@@ -2079,22 +2079,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 127,42</t>
+          <t>-36,69; 120,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-90,3; 26,84</t>
+          <t>-90,71; 27,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-86,72; 9,52</t>
+          <t>-88,68; -9,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,63; 57,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-86,22; 128,64</t>
+          <t>-88,12; 70,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 47,71</t>
+          <t>-51,91; 43,22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-90,79; -21,3</t>
+          <t>-90,83; -19,82</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-81,57; -17,02</t>
+          <t>-84,25; -30,6</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>6,26</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>2,77</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 3,68</t>
+          <t>-40,33; 2,87</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-41,69; -3,5</t>
+          <t>-41,74; -4,54</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 29,32</t>
+          <t>-24,13; 29,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 30,53</t>
+          <t>-4,26; 32,7</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 8,17</t>
+          <t>-12,99; 8,38</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 21,97</t>
+          <t>-6,42; 23,33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 12,5</t>
+          <t>-19,15; 8,92</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-23,97; -0,67</t>
+          <t>-23,43; -0,54</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 18,29</t>
+          <t>-12,28; 18,04</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>145,04%</t>
+          <t>147,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -2295,17 +2295,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 85,51</t>
+          <t>-100,0; 59,34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,38</t>
+          <t>-100,0; 25,27</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,31; 194,98</t>
+          <t>-68,45; 209,07</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-84,19; 160,1</t>
+          <t>-87,42; 114,41</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,3</t>
+          <t>-100,0; 25,33</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 265,94</t>
+          <t>-51,88; 246,35</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-8,74</t>
+          <t>-9,58</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-7,5</t>
+          <t>-7,97</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-21,42; -1,31</t>
+          <t>-20,7; -0,31</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-27,45; -7,22</t>
+          <t>-27,08; -7,69</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 2,29</t>
+          <t>-19,46; 1,89</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 1,39</t>
+          <t>-13,74; 1,11</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 4,11</t>
+          <t>-11,57; 3,76</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 3,43</t>
+          <t>-11,41; 2,99</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-15,58; -1,8</t>
+          <t>-15,17; -1,8</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -4,96</t>
+          <t>-18,4; -4,72</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -0,9</t>
+          <t>-15,38; -1,07</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-27,25%</t>
+          <t>-29,84%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-27,0%</t>
+          <t>-29,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-33,21%</t>
+          <t>-35,28%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-52,67; -3,67</t>
+          <t>-51,9; -1,31</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-70,74; -27,67</t>
+          <t>-70,67; -28,47</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-50,75; 8,85</t>
+          <t>-51,93; 7,26</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 34,13</t>
+          <t>-80,15; 37,66</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 82,98</t>
+          <t>-69,68; 67,8</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-66,54; 66,45</t>
+          <t>-67,18; 63,78</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-55,78; -9,81</t>
+          <t>-55,48; -9,32</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-67,15; -25,78</t>
+          <t>-67,4; -25,46</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-53,97; -4,4</t>
+          <t>-54,36; -3,97</t>
         </is>
       </c>
     </row>
